--- a/r5-TC-FHIR-AG-Messaging-R5-main/all-profiles.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T09:37:24+00:00</t>
+    <t>2026-01-28T12:34:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Messaging-R5-main/all-profiles.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T12:34:00+00:00</t>
+    <t>2026-01-30T08:45:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -612,7 +612,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-uuid-only:fullUrl must be a valid UUID {fullUrl.matches('urn:uuid:[0-9a-f]{8}-[0-9a-f]{4}-[0-9a-f]{4}-[0-9a-f]{4}-[0-9a-f]{12}')}</t>
+uuid-only:fullUrl must be a valid UUID {value.matches('^urn:uuid:[0-9a-f]{8}-[0-9a-f]{4}-[0-9a-f]{4}-[0-9a-f]{4}-[0-9a-f]{12}$')}</t>
   </si>
   <si>
     <t>Bundle.entry.resource</t>

--- a/r5-TC-FHIR-AG-Messaging-R5-main/all-profiles.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T14:50:43+00:00</t>
+    <t>2026-03-18T15:56:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2486,126 +2486,126 @@
     <t>MessageHeader.destination.receiver</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-organization)
+</t>
+  </si>
+  <si>
+    <t>Intended "real-world" recipient for the data</t>
+  </si>
+  <si>
+    <t>Allows data conveyed by a message to be addressed to a particular person or department when routing to a specific application isn't sufficient.</t>
+  </si>
+  <si>
+    <t>Allows routing beyond just the application level.</t>
+  </si>
+  <si>
+    <t>MessageHeader.sender</t>
+  </si>
+  <si>
+    <t>Real world sender of the message</t>
+  </si>
+  <si>
+    <t>Identifies the sending system to allow the use of a trust relationship.</t>
+  </si>
+  <si>
+    <t>Use case is for where a (trusted) sending system is responsible for multiple organizations, and therefore cannot differentiate based on source endpoint / authentication alone. Proposing to remove and rely on Task to convey this information.</t>
+  </si>
+  <si>
+    <t>MessageHeader.author</t>
+  </si>
+  <si>
+    <t>The source of the decision</t>
+  </si>
+  <si>
+    <t>The logical author of the message - the personor device that decided the described event should happen. When there is more than one candidate, pick the most proximal to the MessageHeader. Can provide other authors in extensions.</t>
+  </si>
+  <si>
+    <t>Usually only for the request but can be used in a response.Proposing to remove and rely on Task to convey this information.</t>
+  </si>
+  <si>
+    <t>Need to know for audit/traceback requirements and possibly for authorization.</t>
+  </si>
+  <si>
+    <t>MessageHeader.source</t>
+  </si>
+  <si>
+    <t>Message source application</t>
+  </si>
+  <si>
+    <t>The source application from which this message originated.</t>
+  </si>
+  <si>
+    <t>Allows replies, supports audit.</t>
+  </si>
+  <si>
+    <t>MessageHeader.source.id</t>
+  </si>
+  <si>
+    <t>MessageHeader.source.extension</t>
+  </si>
+  <si>
+    <t>MessageHeader.source.modifierExtension</t>
+  </si>
+  <si>
+    <t>MessageHeader.source.endpoint[x]</t>
+  </si>
+  <si>
+    <t>Actual source address or Endpoint resource</t>
+  </si>
+  <si>
+    <t>Identifies the routing target to send acknowledgements to.</t>
+  </si>
+  <si>
+    <t>Identifies where to send responses, may influence security permissions.</t>
+  </si>
+  <si>
+    <t>MessageHeader.source.name</t>
+  </si>
+  <si>
+    <t>Human-readable name for the source system.</t>
+  </si>
+  <si>
+    <t>May be used to support audit.</t>
+  </si>
+  <si>
+    <t>MessageHeader.source.software</t>
+  </si>
+  <si>
+    <t>Name of software running the system</t>
+  </si>
+  <si>
+    <t>May include configuration or other information useful in debugging.</t>
+  </si>
+  <si>
+    <t>Supports audit and possibly interface engine behavior.</t>
+  </si>
+  <si>
+    <t>MessageHeader.source.version</t>
+  </si>
+  <si>
+    <t>Version of software running</t>
+  </si>
+  <si>
+    <t>Can convey versions of multiple systems in situations where a message passes through multiple hands.</t>
+  </si>
+  <si>
+    <t>MessageHeader.source.contact</t>
+  </si>
+  <si>
+    <t>Human contact for problems</t>
+  </si>
+  <si>
+    <t>An e-mail, phone, website or other contact point to use to resolve issues with message communications.</t>
+  </si>
+  <si>
+    <t>Allows escalation of technical issues.</t>
+  </si>
+  <si>
+    <t>MessageHeader.responsible</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reference(Practitioner|5.0.0|PractitionerRole|5.0.0|Organization|5.0.0)
 </t>
-  </si>
-  <si>
-    <t>Intended "real-world" recipient for the data</t>
-  </si>
-  <si>
-    <t>Allows data conveyed by a message to be addressed to a particular person or department when routing to a specific application isn't sufficient.</t>
-  </si>
-  <si>
-    <t>Allows routing beyond just the application level.</t>
-  </si>
-  <si>
-    <t>MessageHeader.sender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|5.0.0|PractitionerRole|5.0.0|Device|5.0.0|Organization|5.0.0)
-</t>
-  </si>
-  <si>
-    <t>Real world sender of the message</t>
-  </si>
-  <si>
-    <t>Identifies the sending system to allow the use of a trust relationship.</t>
-  </si>
-  <si>
-    <t>Use case is for where a (trusted) sending system is responsible for multiple organizations, and therefore cannot differentiate based on source endpoint / authentication alone. Proposing to remove and rely on Task to convey this information.</t>
-  </si>
-  <si>
-    <t>MessageHeader.author</t>
-  </si>
-  <si>
-    <t>The source of the decision</t>
-  </si>
-  <si>
-    <t>The logical author of the message - the personor device that decided the described event should happen. When there is more than one candidate, pick the most proximal to the MessageHeader. Can provide other authors in extensions.</t>
-  </si>
-  <si>
-    <t>Usually only for the request but can be used in a response.Proposing to remove and rely on Task to convey this information.</t>
-  </si>
-  <si>
-    <t>Need to know for audit/traceback requirements and possibly for authorization.</t>
-  </si>
-  <si>
-    <t>MessageHeader.source</t>
-  </si>
-  <si>
-    <t>Message source application</t>
-  </si>
-  <si>
-    <t>The source application from which this message originated.</t>
-  </si>
-  <si>
-    <t>Allows replies, supports audit.</t>
-  </si>
-  <si>
-    <t>MessageHeader.source.id</t>
-  </si>
-  <si>
-    <t>MessageHeader.source.extension</t>
-  </si>
-  <si>
-    <t>MessageHeader.source.modifierExtension</t>
-  </si>
-  <si>
-    <t>MessageHeader.source.endpoint[x]</t>
-  </si>
-  <si>
-    <t>Actual source address or Endpoint resource</t>
-  </si>
-  <si>
-    <t>Identifies the routing target to send acknowledgements to.</t>
-  </si>
-  <si>
-    <t>Identifies where to send responses, may influence security permissions.</t>
-  </si>
-  <si>
-    <t>MessageHeader.source.name</t>
-  </si>
-  <si>
-    <t>Human-readable name for the source system.</t>
-  </si>
-  <si>
-    <t>May be used to support audit.</t>
-  </si>
-  <si>
-    <t>MessageHeader.source.software</t>
-  </si>
-  <si>
-    <t>Name of software running the system</t>
-  </si>
-  <si>
-    <t>May include configuration or other information useful in debugging.</t>
-  </si>
-  <si>
-    <t>Supports audit and possibly interface engine behavior.</t>
-  </si>
-  <si>
-    <t>MessageHeader.source.version</t>
-  </si>
-  <si>
-    <t>Version of software running</t>
-  </si>
-  <si>
-    <t>Can convey versions of multiple systems in situations where a message passes through multiple hands.</t>
-  </si>
-  <si>
-    <t>MessageHeader.source.contact</t>
-  </si>
-  <si>
-    <t>Human contact for problems</t>
-  </si>
-  <si>
-    <t>An e-mail, phone, website or other contact point to use to resolve issues with message communications.</t>
-  </si>
-  <si>
-    <t>Allows escalation of technical issues.</t>
-  </si>
-  <si>
-    <t>MessageHeader.responsible</t>
   </si>
   <si>
     <t>Final responsibility for event</t>
@@ -10377,7 +10377,7 @@
         <v>83</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>23</v>
@@ -10587,7 +10587,7 @@
         <v>83</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J56" t="s" s="2">
         <v>23</v>
@@ -14161,7 +14161,7 @@
         <v>83</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J90" t="s" s="2">
         <v>23</v>
@@ -18440,7 +18440,7 @@
         <v>83</v>
       </c>
       <c r="I131" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J131" t="s" s="2">
         <v>23</v>
@@ -21568,7 +21568,7 @@
         <v>83</v>
       </c>
       <c r="I161" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J161" t="s" s="2">
         <v>23</v>
@@ -23034,7 +23034,7 @@
         <v>83</v>
       </c>
       <c r="I175" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J175" t="s" s="2">
         <v>23</v>
@@ -23246,7 +23246,7 @@
         <v>83</v>
       </c>
       <c r="I177" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J177" t="s" s="2">
         <v>23</v>
@@ -24302,7 +24302,7 @@
         <v>83</v>
       </c>
       <c r="I187" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J187" t="s" s="2">
         <v>23</v>
@@ -24407,7 +24407,7 @@
         <v>83</v>
       </c>
       <c r="I188" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J188" t="s" s="2">
         <v>23</v>
@@ -24416,16 +24416,16 @@
         <v>84</v>
       </c>
       <c r="L188" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="M188" t="s" s="2">
         <v>793</v>
       </c>
-      <c r="M188" t="s" s="2">
+      <c r="N188" t="s" s="2">
         <v>794</v>
       </c>
-      <c r="N188" t="s" s="2">
+      <c r="O188" t="s" s="2">
         <v>795</v>
-      </c>
-      <c r="O188" t="s" s="2">
-        <v>796</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>791</v>
@@ -24497,10 +24497,10 @@
         <v>710</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D189" s="2"/>
       <c r="E189" t="s" s="2">
@@ -24514,7 +24514,7 @@
         <v>83</v>
       </c>
       <c r="I189" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J189" t="s" s="2">
         <v>23</v>
@@ -24523,19 +24523,19 @@
         <v>84</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="M189" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="N189" t="s" s="2">
         <v>798</v>
       </c>
-      <c r="N189" t="s" s="2">
+      <c r="O189" t="s" s="2">
         <v>799</v>
       </c>
-      <c r="O189" t="s" s="2">
+      <c r="P189" t="s" s="2">
         <v>800</v>
-      </c>
-      <c r="P189" t="s" s="2">
-        <v>801</v>
       </c>
       <c r="Q189" t="s" s="2">
         <v>23</v>
@@ -24584,7 +24584,7 @@
         <v>23</v>
       </c>
       <c r="AG189" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AH189" t="s" s="2">
         <v>76</v>
@@ -24604,10 +24604,10 @@
         <v>710</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D190" s="2"/>
       <c r="E190" t="s" s="2">
@@ -24633,14 +24633,14 @@
         <v>138</v>
       </c>
       <c r="M190" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="N190" t="s" s="2">
         <v>803</v>
-      </c>
-      <c r="N190" t="s" s="2">
-        <v>804</v>
       </c>
       <c r="O190" s="2"/>
       <c r="P190" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="Q190" t="s" s="2">
         <v>23</v>
@@ -24689,7 +24689,7 @@
         <v>23</v>
       </c>
       <c r="AG190" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="AH190" t="s" s="2">
         <v>83</v>
@@ -24709,10 +24709,10 @@
         <v>710</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D191" s="2"/>
       <c r="E191" t="s" s="2">
@@ -24812,10 +24812,10 @@
         <v>710</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="D192" s="2"/>
       <c r="E192" t="s" s="2">
@@ -24917,10 +24917,10 @@
         <v>710</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D193" s="2"/>
       <c r="E193" t="s" s="2">
@@ -25024,10 +25024,10 @@
         <v>710</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="D194" s="2"/>
       <c r="E194" t="s" s="2">
@@ -25053,16 +25053,16 @@
         <v>773</v>
       </c>
       <c r="M194" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="N194" t="s" s="2">
         <v>810</v>
-      </c>
-      <c r="N194" t="s" s="2">
-        <v>811</v>
       </c>
       <c r="O194" t="s" s="2">
         <v>776</v>
       </c>
       <c r="P194" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="Q194" t="s" s="2">
         <v>23</v>
@@ -25111,7 +25111,7 @@
         <v>23</v>
       </c>
       <c r="AG194" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="AH194" t="s" s="2">
         <v>76</v>
@@ -25131,10 +25131,10 @@
         <v>710</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="D195" s="2"/>
       <c r="E195" t="s" s="2">
@@ -25148,7 +25148,7 @@
         <v>83</v>
       </c>
       <c r="I195" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J195" t="s" s="2">
         <v>23</v>
@@ -25163,11 +25163,11 @@
         <v>779</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="Q195" t="s" s="2">
         <v>23</v>
@@ -25216,7 +25216,7 @@
         <v>23</v>
       </c>
       <c r="AG195" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="AH195" t="s" s="2">
         <v>76</v>
@@ -25236,10 +25236,10 @@
         <v>710</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="D196" s="2"/>
       <c r="E196" t="s" s="2">
@@ -25253,7 +25253,7 @@
         <v>83</v>
       </c>
       <c r="I196" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J196" t="s" s="2">
         <v>23</v>
@@ -25265,14 +25265,14 @@
         <v>144</v>
       </c>
       <c r="M196" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="N196" t="s" s="2">
         <v>817</v>
-      </c>
-      <c r="N196" t="s" s="2">
-        <v>818</v>
       </c>
       <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="Q196" t="s" s="2">
         <v>23</v>
@@ -25321,7 +25321,7 @@
         <v>23</v>
       </c>
       <c r="AG196" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="AH196" t="s" s="2">
         <v>76</v>
@@ -25341,10 +25341,10 @@
         <v>710</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="D197" s="2"/>
       <c r="E197" t="s" s="2">
@@ -25358,7 +25358,7 @@
         <v>83</v>
       </c>
       <c r="I197" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J197" t="s" s="2">
         <v>23</v>
@@ -25370,14 +25370,14 @@
         <v>144</v>
       </c>
       <c r="M197" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="N197" t="s" s="2">
         <v>821</v>
-      </c>
-      <c r="N197" t="s" s="2">
-        <v>822</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="Q197" t="s" s="2">
         <v>23</v>
@@ -25426,7 +25426,7 @@
         <v>23</v>
       </c>
       <c r="AG197" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AH197" t="s" s="2">
         <v>76</v>
@@ -25446,10 +25446,10 @@
         <v>710</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D198" s="2"/>
       <c r="E198" t="s" s="2">
@@ -25463,7 +25463,7 @@
         <v>83</v>
       </c>
       <c r="I198" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J198" t="s" s="2">
         <v>23</v>
@@ -25475,14 +25475,14 @@
         <v>678</v>
       </c>
       <c r="M198" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="N198" t="s" s="2">
         <v>824</v>
-      </c>
-      <c r="N198" t="s" s="2">
-        <v>825</v>
       </c>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="Q198" t="s" s="2">
         <v>23</v>
@@ -25531,7 +25531,7 @@
         <v>23</v>
       </c>
       <c r="AG198" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="AH198" t="s" s="2">
         <v>76</v>
@@ -25551,10 +25551,10 @@
         <v>710</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D199" s="2"/>
       <c r="E199" t="s" s="2">
@@ -25577,7 +25577,7 @@
         <v>84</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>788</v>
+        <v>827</v>
       </c>
       <c r="M199" t="s" s="2">
         <v>828</v>
@@ -25586,10 +25586,10 @@
         <v>829</v>
       </c>
       <c r="O199" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="P199" t="s" s="2">
         <v>800</v>
-      </c>
-      <c r="P199" t="s" s="2">
-        <v>801</v>
       </c>
       <c r="Q199" t="s" s="2">
         <v>23</v>
@@ -25638,7 +25638,7 @@
         <v>23</v>
       </c>
       <c r="AG199" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="AH199" t="s" s="2">
         <v>76</v>
@@ -26624,7 +26624,7 @@
         <v>83</v>
       </c>
       <c r="I209" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J209" t="s" s="2">
         <v>23</v>

--- a/r5-TC-FHIR-AG-Messaging-R5-main/all-profiles.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T15:56:08+00:00</t>
+    <t>2026-04-09T09:35:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Messaging-R5-main/all-profiles.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T09:35:35+00:00</t>
+    <t>2026-04-09T10:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Messaging-R5-main/all-profiles.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T10:04:08+00:00</t>
+    <t>2026-04-09T11:10:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Messaging-R5-main/all-profiles.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T11:10:35+00:00</t>
+    <t>2026-04-09T11:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Messaging-R5-main/all-profiles.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T11:58:42+00:00</t>
+    <t>2026-05-06T12:27:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
